--- a/Scripts_inesdattatreya/data_output/session_2025-09with_classes.xlsx
+++ b/Scripts_inesdattatreya/data_output/session_2025-09with_classes.xlsx
@@ -489,7 +489,7 @@
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>class</t>
+          <t>lca_class</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="Z2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="Z3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="Z4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="Z5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -1095,7 +1095,7 @@
         </is>
       </c>
       <c r="Z6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -1216,7 +1216,7 @@
         </is>
       </c>
       <c r="Z7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -1337,7 +1337,7 @@
         </is>
       </c>
       <c r="Z8">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -1458,7 +1458,7 @@
         </is>
       </c>
       <c r="Z9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -1579,7 +1579,7 @@
         </is>
       </c>
       <c r="Z10">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1700,7 +1700,7 @@
         </is>
       </c>
       <c r="Z11">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="Z12">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1942,7 +1942,7 @@
         </is>
       </c>
       <c r="Z13">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Z14">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -2184,7 +2184,7 @@
         </is>
       </c>
       <c r="Z15">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="Z16">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -2426,7 +2426,7 @@
         </is>
       </c>
       <c r="Z17">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -2547,7 +2547,7 @@
         </is>
       </c>
       <c r="Z18">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="Z19">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Z20">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -2910,7 +2910,7 @@
         </is>
       </c>
       <c r="Z21">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="Z22">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -3152,7 +3152,7 @@
         </is>
       </c>
       <c r="Z23">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="Z24">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -3394,7 +3394,7 @@
         </is>
       </c>
       <c r="Z25">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="Z26">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -3636,7 +3636,7 @@
         </is>
       </c>
       <c r="Z27">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -3662,7 +3662,7 @@
         </is>
       </c>
       <c r="Z28">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Z31">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -4146,7 +4146,7 @@
         </is>
       </c>
       <c r="Z32">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -4388,7 +4388,7 @@
         </is>
       </c>
       <c r="Z34">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -4509,7 +4509,7 @@
         </is>
       </c>
       <c r="Z35">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -4993,7 +4993,7 @@
         </is>
       </c>
       <c r="Z39">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -5235,7 +5235,7 @@
         </is>
       </c>
       <c r="Z41">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -5477,7 +5477,7 @@
         </is>
       </c>
       <c r="Z43">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -5598,7 +5598,7 @@
         </is>
       </c>
       <c r="Z44">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -5840,7 +5840,7 @@
         </is>
       </c>
       <c r="Z46">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="Z48">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -6324,7 +6324,7 @@
         </is>
       </c>
       <c r="Z50">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -6566,7 +6566,7 @@
         </is>
       </c>
       <c r="Z52">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53">
@@ -6687,7 +6687,7 @@
         </is>
       </c>
       <c r="Z53">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
